--- a/StructureDefinition-mii-lm-diagnose.xlsx
+++ b/StructureDefinition-mii-lm-diagnose.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="225">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2026.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-09</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,6 +90,9 @@
     <t>Purpose</t>
   </si>
   <si>
+    <t>Define the information model for diagnoses independently of a concrete FHIR resource representation.</t>
+  </si>
+  <si>
     <t>Copyright</t>
   </si>
   <si>
@@ -114,9 +120,6 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>Derivation</t>
   </si>
   <si>
@@ -232,9 +235,6 @@
   </si>
   <si>
     <t>Mapping: Diagnose LogicalModel FHIR Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: RIM Mapping</t>
   </si>
   <si>
     <t>Diagnose</t>
@@ -267,9 +267,6 @@
 </t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Diagnose.id</t>
   </si>
   <si>
@@ -366,9 +363,6 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Diagnose.ICD10GMDiagnoseKodiert.Diagnosecode</t>
@@ -900,79 +894,83 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>3</v>
@@ -980,26 +978,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1009,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL54"/>
+  <dimension ref="A1:AK54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.1875" customWidth="true" bestFit="true"/>
@@ -1048,122 +1046,118 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="152.92578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>72</v>
-      </c>
-      <c r="AL1" t="s" s="1">
         <v>73</v>
       </c>
     </row>
@@ -1201,7 +1195,7 @@
         <v>79</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1269,16 +1263,13 @@
       <c r="AK2" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AL2" t="s" s="2">
-        <v>83</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1289,25 +1280,25 @@
         <v>76</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1358,13 +1349,13 @@
         <v>75</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>75</v>
@@ -1374,21 +1365,18 @@
       </c>
       <c r="AK3" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL3" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1407,16 +1395,16 @@
         <v>75</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M4" t="s" s="2">
+      <c r="N4" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1454,19 +1442,19 @@
         <v>75</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
@@ -1478,21 +1466,18 @@
         <v>75</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL4" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1503,7 +1488,7 @@
         <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>75</v>
@@ -1515,13 +1500,13 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1572,13 +1557,13 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>75</v>
@@ -1587,18 +1572,15 @@
         <v>82</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1609,25 +1591,25 @@
         <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1678,13 +1660,13 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>75</v>
@@ -1694,21 +1676,18 @@
       </c>
       <c r="AK6" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL6" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1727,16 +1706,16 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1774,19 +1753,19 @@
         <v>75</v>
       </c>
       <c r="AB7" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC7" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC7" t="s" s="2">
+      <c r="AD7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE7" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE7" t="s" s="2">
+      <c r="AF7" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1798,25 +1777,22 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1829,25 +1805,25 @@
         <v>75</v>
       </c>
       <c r="I8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="J8" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O8" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>75</v>
@@ -1896,7 +1872,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1908,21 +1884,18 @@
         <v>75</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1930,10 +1903,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>75</v>
@@ -1945,13 +1918,13 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2002,13 +1975,13 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>75</v>
@@ -2017,18 +1990,15 @@
         <v>75</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>75</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2039,7 +2009,7 @@
         <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>75</v>
@@ -2051,13 +2021,13 @@
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2108,13 +2078,13 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>75</v>
@@ -2123,18 +2093,15 @@
         <v>75</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>75</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2145,7 +2112,7 @@
         <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>75</v>
@@ -2157,13 +2124,13 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2214,13 +2181,13 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>75</v>
@@ -2229,18 +2196,15 @@
         <v>75</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>75</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2251,7 +2215,7 @@
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>75</v>
@@ -2263,13 +2227,13 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2320,13 +2284,13 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>75</v>
@@ -2335,18 +2299,15 @@
         <v>75</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2357,7 +2318,7 @@
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>75</v>
@@ -2369,13 +2330,13 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2426,13 +2387,13 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>75</v>
@@ -2441,18 +2402,15 @@
         <v>82</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2463,25 +2421,25 @@
         <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K14" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K14" t="s" s="2">
+      <c r="L14" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2532,13 +2490,13 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>75</v>
@@ -2548,21 +2506,18 @@
       </c>
       <c r="AK14" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2581,16 +2536,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2628,19 +2583,19 @@
         <v>75</v>
       </c>
       <c r="AB15" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC15" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC15" t="s" s="2">
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
+      <c r="AF15" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2652,25 +2607,22 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2683,25 +2635,25 @@
         <v>75</v>
       </c>
       <c r="I16" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="J16" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>75</v>
@@ -2750,7 +2702,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2762,21 +2714,18 @@
         <v>75</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2784,10 +2733,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>75</v>
@@ -2799,13 +2748,13 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2856,33 +2805,30 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2893,7 +2839,7 @@
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>75</v>
@@ -2905,13 +2851,13 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2962,13 +2908,13 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>75</v>
@@ -2977,18 +2923,15 @@
         <v>82</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>75</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2999,25 +2942,25 @@
         <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K19" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K19" t="s" s="2">
+      <c r="L19" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3068,13 +3011,13 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>75</v>
@@ -3084,21 +3027,18 @@
       </c>
       <c r="AK19" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3117,16 +3057,16 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3164,19 +3104,19 @@
         <v>75</v>
       </c>
       <c r="AB20" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC20" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC20" t="s" s="2">
+      <c r="AD20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE20" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE20" t="s" s="2">
+      <c r="AF20" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3188,25 +3128,22 @@
         <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3219,25 +3156,25 @@
         <v>75</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>75</v>
@@ -3286,7 +3223,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3298,21 +3235,18 @@
         <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3320,10 +3254,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>75</v>
@@ -3335,13 +3269,13 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3392,33 +3326,30 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3429,7 +3360,7 @@
         <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>75</v>
@@ -3441,13 +3372,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3498,13 +3429,13 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>75</v>
@@ -3513,18 +3444,15 @@
         <v>82</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>75</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3535,25 +3463,25 @@
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K24" t="s" s="2">
+      <c r="L24" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3604,13 +3532,13 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>75</v>
@@ -3620,21 +3548,18 @@
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3653,16 +3578,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3700,19 +3625,19 @@
         <v>75</v>
       </c>
       <c r="AB25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC25" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC25" t="s" s="2">
+      <c r="AD25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE25" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE25" t="s" s="2">
+      <c r="AF25" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3724,25 +3649,22 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -3755,25 +3677,25 @@
         <v>75</v>
       </c>
       <c r="I26" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="J26" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -3822,7 +3744,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3834,21 +3756,18 @@
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3856,10 +3775,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
@@ -3871,13 +3790,13 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3928,33 +3847,30 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3977,13 +3893,13 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4034,7 +3950,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4049,18 +3965,15 @@
         <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4071,25 +3984,25 @@
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K29" t="s" s="2">
+      <c r="L29" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4140,13 +4053,13 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>75</v>
@@ -4156,21 +4069,18 @@
       </c>
       <c r="AK29" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4189,16 +4099,16 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4236,19 +4146,19 @@
         <v>75</v>
       </c>
       <c r="AB30" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC30" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC30" t="s" s="2">
+      <c r="AD30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE30" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE30" t="s" s="2">
+      <c r="AF30" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4260,25 +4170,22 @@
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4291,25 +4198,25 @@
         <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="J31" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O31" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -4358,7 +4265,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4370,21 +4277,18 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4392,10 +4296,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>75</v>
@@ -4407,13 +4311,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4464,13 +4368,13 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>75</v>
@@ -4479,18 +4383,15 @@
         <v>75</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>75</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4513,13 +4414,13 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4570,7 +4471,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4585,18 +4486,15 @@
         <v>75</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4607,25 +4505,25 @@
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K34" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="L34" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4676,13 +4574,13 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
@@ -4691,18 +4589,15 @@
         <v>75</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>75</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4725,13 +4620,13 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4782,7 +4677,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -4797,18 +4692,15 @@
         <v>75</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>75</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4819,7 +4711,7 @@
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>75</v>
@@ -4831,13 +4723,13 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4888,13 +4780,13 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>75</v>
@@ -4903,18 +4795,15 @@
         <v>75</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>75</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4925,7 +4814,7 @@
         <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>75</v>
@@ -4937,13 +4826,13 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4994,13 +4883,13 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>75</v>
@@ -5009,18 +4898,15 @@
         <v>82</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>75</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5031,25 +4917,25 @@
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K38" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K38" t="s" s="2">
+      <c r="L38" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5100,13 +4986,13 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>75</v>
@@ -5116,21 +5002,18 @@
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5149,16 +5032,16 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5196,19 +5079,19 @@
         <v>75</v>
       </c>
       <c r="AB39" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC39" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC39" t="s" s="2">
+      <c r="AD39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE39" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE39" t="s" s="2">
+      <c r="AF39" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5220,25 +5103,22 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5251,25 +5131,25 @@
         <v>75</v>
       </c>
       <c r="I40" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="J40" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O40" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -5318,7 +5198,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5330,21 +5210,18 @@
         <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5355,7 +5232,7 @@
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
@@ -5367,13 +5244,13 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5424,13 +5301,13 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>75</v>
@@ -5439,18 +5316,15 @@
         <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>75</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5461,25 +5335,25 @@
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K42" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K42" t="s" s="2">
+      <c r="L42" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5530,13 +5404,13 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>75</v>
@@ -5546,21 +5420,18 @@
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -5579,16 +5450,16 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5626,19 +5497,19 @@
         <v>75</v>
       </c>
       <c r="AB43" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC43" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC43" t="s" s="2">
+      <c r="AD43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE43" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE43" t="s" s="2">
+      <c r="AF43" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -5650,25 +5521,22 @@
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -5681,25 +5549,25 @@
         <v>75</v>
       </c>
       <c r="I44" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="J44" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -5748,7 +5616,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5760,21 +5628,18 @@
         <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5785,7 +5650,7 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
@@ -5797,13 +5662,13 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5854,13 +5719,13 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>75</v>
@@ -5869,18 +5734,15 @@
         <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>75</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5891,7 +5753,7 @@
         <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>75</v>
@@ -5903,13 +5765,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5960,33 +5822,30 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK46" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6009,13 +5868,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6066,7 +5925,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6083,16 +5942,13 @@
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AL47" t="s" s="2">
-        <v>75</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6103,25 +5959,25 @@
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K48" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K48" t="s" s="2">
+      <c r="L48" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6172,13 +6028,13 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>75</v>
@@ -6188,21 +6044,18 @@
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6221,16 +6074,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6268,19 +6121,19 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC49" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC49" t="s" s="2">
+      <c r="AD49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE49" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE49" t="s" s="2">
+      <c r="AF49" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6292,25 +6145,22 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6323,25 +6173,25 @@
         <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="J50" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -6390,7 +6240,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6402,21 +6252,18 @@
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6427,7 +6274,7 @@
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>75</v>
@@ -6439,13 +6286,13 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6496,33 +6343,30 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK51" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6533,7 +6377,7 @@
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>75</v>
@@ -6545,13 +6389,13 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6602,33 +6446,30 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK52" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6639,7 +6480,7 @@
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>75</v>
@@ -6651,13 +6492,13 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6708,13 +6549,13 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>75</v>
@@ -6723,18 +6564,15 @@
         <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>75</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6742,10 +6580,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -6757,13 +6595,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6814,13 +6652,13 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>75</v>
@@ -6829,10 +6667,7 @@
         <v>75</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-mii-lm-diagnose.xlsx
+++ b/StructureDefinition-mii-lm-diagnose.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="230">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -538,6 +538,22 @@
   </si>
   <si>
     <t>Condition.bodySite</t>
+  </si>
+  <si>
+    <t>Diagnose.DetaillierteAnatomischeStruktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(BodyStructure)
+</t>
+  </si>
+  <si>
+    <t>Detaillierte anatomische Struktur</t>
+  </si>
+  <si>
+    <t>Detaillierte Angaben zu der patientenbezogenen anatomischen Struktur oder Lokalisation, auf die sich die Diagnose bezieht. Das Element kann verwendet werden, wenn die kodierte Angabe der Körperstelle allein nicht die für den Anwendungsfall erforderliche Genauigkeit bietet.</t>
+  </si>
+  <si>
+    <t>Condition.bodySite.extension('http://hl7.org/fhir/StructureDefinition/bodySite').valueReference</t>
   </si>
   <si>
     <t>Diagnose.Freitextbeschreibung</t>
@@ -1007,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK54"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.1875" customWidth="true" bestFit="true"/>
@@ -1020,7 +1036,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="21.45703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4505,7 +4521,7 @@
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>75</v>
@@ -4517,13 +4533,13 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>85</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4580,7 +4596,7 @@
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
@@ -4589,15 +4605,15 @@
         <v>75</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4608,7 +4624,7 @@
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>75</v>
@@ -4623,10 +4639,10 @@
         <v>85</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4677,13 +4693,13 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>75</v>
@@ -4692,15 +4708,15 @@
         <v>75</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4711,7 +4727,7 @@
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>75</v>
@@ -4723,13 +4739,13 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4780,13 +4796,13 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>75</v>
@@ -4795,15 +4811,15 @@
         <v>75</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4826,13 +4842,13 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4883,7 +4899,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -4895,18 +4911,18 @@
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4929,13 +4945,13 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>87</v>
+        <v>190</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4986,7 +5002,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -4998,29 +5014,29 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>75</v>
@@ -5032,17 +5048,15 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5079,31 +5093,31 @@
         <v>75</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5111,14 +5125,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5131,26 +5145,24 @@
         <v>75</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="O40" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -5186,19 +5198,19 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5218,42 +5230,46 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -5301,30 +5317,30 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>193</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5347,13 +5363,13 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>86</v>
+        <v>196</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>87</v>
+        <v>197</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5404,7 +5420,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>88</v>
+        <v>195</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5416,29 +5432,29 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>75</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
@@ -5450,17 +5466,15 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -5497,31 +5511,31 @@
         <v>75</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>75</v>
@@ -5529,14 +5543,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -5549,26 +5563,24 @@
         <v>75</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="O44" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>75</v>
       </c>
@@ -5604,19 +5616,19 @@
         <v>75</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5636,42 +5648,46 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
@@ -5719,30 +5735,30 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>200</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5765,13 +5781,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5822,7 +5838,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -5837,15 +5853,15 @@
         <v>75</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5856,7 +5872,7 @@
         <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>75</v>
@@ -5868,13 +5884,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>101</v>
+        <v>203</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5925,30 +5941,30 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>75</v>
+        <v>208</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5959,7 +5975,7 @@
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>75</v>
@@ -5971,13 +5987,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6028,19 +6044,19 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
@@ -6048,21 +6064,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
@@ -6074,17 +6090,15 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6121,31 +6135,31 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
@@ -6153,14 +6167,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6173,26 +6187,24 @@
         <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="O50" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
       </c>
@@ -6228,19 +6240,19 @@
         <v>75</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6260,42 +6272,46 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
       </c>
@@ -6343,30 +6359,30 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>212</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6392,10 +6408,10 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6446,7 +6462,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6461,15 +6477,15 @@
         <v>75</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6492,10 +6508,10 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>219</v>
@@ -6549,7 +6565,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6580,7 +6596,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>84</v>
@@ -6595,13 +6611,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6655,7 +6671,7 @@
         <v>221</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>84</v>
@@ -6667,7 +6683,110 @@
         <v>75</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-mii-lm-diagnose.xlsx
+++ b/StructureDefinition-mii-lm-diagnose.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="228">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -601,9 +601,6 @@
     <t>Hier kann der Klinisch Relevante Zeitraum beziehungsweise die Lebensphase einer Erkrankung angegeben werden. Datumsangaben zu Diagnosen können in unterschiedlicher Präzision vorhanden sein.</t>
   </si>
   <si>
-    <t>Condition.onset[x]</t>
-  </si>
-  <si>
     <t>Diagnose.KlinischRelevanterZeitraum.id</t>
   </si>
   <si>
@@ -620,9 +617,6 @@
   </si>
   <si>
     <t>Der Zeitraum wird durch zwei Datumsangaben beschrieben, das heißt, von wann bis wann ein Patient an der diagnostizierten Krankheit litt. Über den Zeitraum kann auch ausgedrückt werden, seit wann ein Patient an einer Krankheit leidet, indem nur das Startdatum des Zeitraums angegeben wird. Das Startdatum des Zeitraums kann abweichen von dem Diagnosedatum. Datumsangaben zu Diagnosen können in unterschiedlicher Präzision vorhanden sein.</t>
-  </si>
-  <si>
-    <t>Condition.onsetPeriod</t>
   </si>
   <si>
     <t>Diagnose.KlinischRelevanterZeitraum.Zeitraum.id</t>
@@ -644,7 +638,7 @@
     <t>Startdatum</t>
   </si>
   <si>
-    <t>Condition.onsetPeriod.start</t>
+    <t>Condition.onsetDateTime</t>
   </si>
   <si>
     <t>Diagnose.KlinischRelevanterZeitraum.Zeitraum.bis</t>
@@ -653,7 +647,7 @@
     <t>Enddatum</t>
   </si>
   <si>
-    <t>Condition.onsetPeriod.end</t>
+    <t>Condition.abatementDateTime</t>
   </si>
   <si>
     <t>Diagnose.KlinischRelevanterZeitraum.Lebensphase</t>
@@ -680,7 +674,7 @@
     <t>In welcher Lebensphase die Krankheit began</t>
   </si>
   <si>
-    <t>Condition.onsetPeriod.start.extension('http://fhir.de/StructureDefinition/lebensphase').valueCodeableConcept</t>
+    <t>Condition.onsetAge.extension('http://fhir.de/StructureDefinition/lebensphase').valueCodeableConcept</t>
   </si>
   <si>
     <t>Diagnose.KlinischRelevanterZeitraum.Lebensphase.bis</t>
@@ -689,7 +683,7 @@
     <t>In welcher Lebensphase die Krankheit endete</t>
   </si>
   <si>
-    <t>Condition.onsetPeriod.end.extension('http://fhir.de/StructureDefinition/lebensphase').valueCodeableConcept</t>
+    <t>Condition.abatementAge.extension('http://fhir.de/StructureDefinition/lebensphase').valueCodeableConcept</t>
   </si>
   <si>
     <t>Diagnose.Feststellungsdatum</t>
@@ -5017,15 +5011,15 @@
         <v>82</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>191</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5125,10 +5119,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5230,10 +5224,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5337,10 +5331,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5366,10 +5360,10 @@
         <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5420,7 +5414,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5435,15 +5429,15 @@
         <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>198</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5543,10 +5537,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5648,10 +5642,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5755,10 +5749,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5781,13 +5775,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5838,7 +5832,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -5853,15 +5847,15 @@
         <v>75</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5884,13 +5878,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5941,30 +5935,30 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK47" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>208</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5990,10 +5984,10 @@
         <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6044,7 +6038,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6064,10 +6058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6167,10 +6161,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6272,10 +6266,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6379,10 +6373,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6408,10 +6402,10 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6462,30 +6456,30 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK52" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6511,10 +6505,10 @@
         <v>114</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6565,30 +6559,30 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK53" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6611,13 +6605,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6668,7 +6662,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6683,15 +6677,15 @@
         <v>75</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6714,13 +6708,13 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6771,7 +6765,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -6786,7 +6780,7 @@
         <v>75</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
